--- a/medical_surveys_questionnaires/011_cardiovascular_health_outcomes_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/011_cardiovascular_health_outcomes_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -904,8 +904,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -933,12 +933,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'male',_'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Male', 'value': 'male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'female',_'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Female', 'value': 'female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'non-binary',_'value':_'non_binary'}</t>
+          <t>non-binary</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Non-binary', 'value': 'non_binary'}</t>
+          <t>Non-binary</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'prefer_not_to_say',_'value':_'skip'}</t>
+          <t>prefer_not_to_say</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Prefer not to say', 'value': 'skip'}</t>
+          <t>Prefer not to say</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure',_'value':_'unsure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure', 'value': 'unsure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'never_smoked',_'value':_'never'}</t>
+          <t>never_smoked</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Never Smoked', 'value': 'never'}</t>
+          <t>Never Smoked</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'former_smoker_(quit_&gt;1_year_ago)',_'value':_'former'}</t>
+          <t>former_smoker_(quit_&gt;1_year_ago)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Former Smoker (Quit &gt;1 year ago)', 'value': 'former'}</t>
+          <t>Former Smoker (Quit &gt;1 year ago)</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'recent_quitter_(quit_&lt;1_year_ago)',_'value':_'recent_quit'}</t>
+          <t>recent_quitter_(quit_&lt;1_year_ago)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Recent Quitter (Quit &lt;1 year ago)', 'value': 'recent_quit'}</t>
+          <t>Recent Quitter (Quit &lt;1 year ago)</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'current_smoker',_'value':_'current'}</t>
+          <t>current_smoker</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Current Smoker', 'value': 'current'}</t>
+          <t>Current Smoker</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'never',_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Never', 'value': 'never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'rarely_(1-2_times)',_'value':_'rarely'}</t>
+          <t>rarely_(1-2_times)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely (1-2 times)', 'value': 'rarely'}</t>
+          <t>Rarely (1-2 times)</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes_(weekly)',_'value':_'sometimes'}</t>
+          <t>sometimes_(weekly)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes (Weekly)', 'value': 'sometimes'}</t>
+          <t>Sometimes (Weekly)</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'often_(daily)',_'value':_'often'}</t>
+          <t>often_(daily)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Often (Daily)', 'value': 'often'}</t>
+          <t>Often (Daily)</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'never',_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Never', 'value': 'never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely', 'value': 'rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes',_'value':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes', 'value': 'sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'often',_'value':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Often', 'value': 'often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
